--- a/backend/data/campaign_77_leads.xlsx
+++ b/backend/data/campaign_77_leads.xlsx
@@ -104,7 +104,7 @@
     <t>https://synchronypharmacy.com/</t>
   </si>
   <si>
-    <t>sakshi.gupta@neutrinotechlabs.com</t>
+    <t>pranav.parvekar@neutrinotechlabs.com</t>
   </si>
   <si>
     <t>Columbus</t>
